--- a/VaydeerMacropad.Mouse.VisualStudio.Template.xlsx
+++ b/VaydeerMacropad.Mouse.VisualStudio.Template.xlsx
@@ -548,6 +548,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -555,6 +560,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -563,9 +571,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -577,39 +594,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,16 +976,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>103320</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>41612</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>494002</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>64216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>197386</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>87178</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>95492</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>180813</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1002,8 +1002,46 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4087676" y="1223358"/>
-          <a:ext cx="2247685" cy="807566"/>
+          <a:off x="494002" y="2398648"/>
+          <a:ext cx="2975600" cy="1069097"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>95463</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>39390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>497237</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9687</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4402700" y="1221136"/>
+          <a:ext cx="1622266" cy="2075483"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1370,13 +1408,13 @@
       <c r="C3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="39" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="33" t="s">
@@ -1385,10 +1423,10 @@
       <c r="K3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="49" t="s">
+      <c r="N3" s="53" t="s">
         <v>19</v>
       </c>
       <c r="O3" s="30" t="s">
@@ -1403,12 +1441,12 @@
       <c r="C4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="35"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="51" t="s">
+      <c r="E4" s="45"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="38"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="34" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1449,13 +1487,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="37" t="s">
         <v>13</v>
       </c>
       <c r="M6" s="31" t="s">
@@ -1464,7 +1502,7 @@
       <c r="N6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="34" t="s">
+      <c r="O6" s="37" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1476,16 +1514,16 @@
         <v>5</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="35"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="38"/>
       <c r="M7" s="32" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="O7" s="45"/>
+      <c r="O7" s="55"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
@@ -1520,22 +1558,22 @@
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="8"/>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="47" t="s">
+      <c r="N9" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="36" t="s">
+      <c r="O9" s="39" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1543,55 +1581,55 @@
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="13"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="53"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="52"/>
-      <c r="O10" s="53"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="40"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="40"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M11" s="54" t="s">
+      <c r="M11" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="54" t="s">
+      <c r="N11" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="55"/>
+      <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M12" s="55" t="s">
+      <c r="M12" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="N12" s="55" t="s">
+      <c r="N12" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="55"/>
+      <c r="O12" s="36"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M13" s="54" t="s">
+      <c r="M13" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M14" s="55" t="s">
+      <c r="M14" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="N14" s="55" t="s">
+      <c r="N14" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="55"/>
+      <c r="O14" s="36"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M15" s="55" t="s">
+      <c r="M15" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="N15" s="55" t="s">
+      <c r="N15" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="O15" s="55"/>
+      <c r="O15" s="36"/>
     </row>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/VaydeerMacropad.Mouse.VisualStudio.Template.xlsx
+++ b/VaydeerMacropad.Mouse.VisualStudio.Template.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
   <si>
     <t>C+5</t>
   </si>
@@ -58,18 +58,12 @@
     <t>F8</t>
   </si>
   <si>
-    <t>Close Win</t>
-  </si>
-  <si>
     <t>Run Test</t>
   </si>
   <si>
     <t>Dbg Test</t>
   </si>
   <si>
-    <t>ExitApp</t>
-  </si>
-  <si>
     <t>Temp</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
     <t>Zeerka</t>
   </si>
   <si>
-    <t>VSCode</t>
-  </si>
-  <si>
     <t>Calc</t>
   </si>
   <si>
@@ -91,9 +82,6 @@
     <t>ClsWin</t>
   </si>
   <si>
-    <t>Pwd</t>
-  </si>
-  <si>
     <t>PrtScn</t>
   </si>
   <si>
@@ -152,6 +140,27 @@
   </si>
   <si>
     <t>Copilot</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>VsCode</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Win</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>App</t>
+  </si>
+  <si>
+    <t>Pwd--</t>
   </si>
 </sst>
 </file>
@@ -453,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -553,12 +562,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -571,10 +574,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -583,31 +622,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -647,7 +665,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F260F60A-DBEE-42CC-E5BD-D375680FC416}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -703,7 +721,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CAA941E0-F4D6-44EA-A8EB-038D50ADF789}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -825,13 +843,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>41355</xdr:colOff>
+      <xdr:colOff>57500</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>529664</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>539898</xdr:colOff>
+      <xdr:colOff>556043</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>84160</xdr:rowOff>
     </xdr:to>
@@ -850,7 +868,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4958838" y="529664"/>
+          <a:off x="4974983" y="529664"/>
           <a:ext cx="498543" cy="545742"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1403,34 +1421,34 @@
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="I3" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="30" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="30" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -1441,13 +1459,13 @@
       <c r="C4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="38"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="54"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="51"/>
       <c r="O4" s="34" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1487,23 +1505,23 @@
         <v>4</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="E6" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="37" t="s">
-        <v>13</v>
+      <c r="E6" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>35</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="O6" s="37" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="O6" s="52" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -1514,16 +1532,18 @@
         <v>5</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="38"/>
+      <c r="E7" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="58"/>
+      <c r="G7" s="54"/>
       <c r="M7" s="32" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="55"/>
+        <v>32</v>
+      </c>
+      <c r="O7" s="53"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="23">
@@ -1558,98 +1578,99 @@
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="8"/>
-      <c r="E9" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="39" t="s">
-        <v>25</v>
+      <c r="E9" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="47" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
       <c r="B10" s="12"/>
       <c r="C10" s="13"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="40"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="40"/>
+      <c r="E10" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="46"/>
+      <c r="G10" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="44"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="48"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M11" s="35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N11" s="35" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="O11" s="36"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M12" s="36" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N12" s="36" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="O12" s="36"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M13" s="35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N13" s="36"/>
       <c r="O13" s="36"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M14" s="36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O14" s="36"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M15" s="36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O15" s="36"/>
     </row>
     <row r="19" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="12">
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="N9:N10"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O6:O7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
